--- a/assets/files/TrackDX-Import-Assistant.xlsx
+++ b/assets/files/TrackDX-Import-Assistant.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,6 +132,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -610,7 +613,7 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>•  Example — a fully filled-in sample sheet showing what correct data looks like.</t>
+          <t>•  Example — a fully filled-in sample sheet showing what correct data looks like, including several relief medications on one episode.</t>
         </is>
       </c>
     </row>
@@ -685,13 +688,18 @@
 Please read the Format Guide and Example tabs carefully, then convert my existing data into that exact layout. Specifically:
 - Create ONE sheet per medical condition I'm tracking, named with the condition's name (max 15 characters, since that's Excel's tab-name rule TrackDX follows).
 - Each sheet needs ONE ROW PER CALENDAR DAY, starting from the earliest date in my data through today — including days with nothing logged (leave those columns blank, but still include the row with the date and 0s where appropriate). This matters for TrackDX's statistics.
-- Follow the exact column headers and order shown in the Example tab: Date, Episode Occurred, Episode Count, Triggers Logged, Trigger Start Time, Trigger End Time, Drinks, then a repeating group of 7 columns per episode that happened that day (Episode 1 Start Time, Episode 1 End Time, Episode 1 Duration (h), Episode 1 Intensity (1-10), Episode 1 Relief Medication, Episode 1 Relief Helped, Episode 1 Suspected Cause — then Episode 2 …, Episode 3 …, etc. if more than one episode ever happens on the same day).
+- Follow the exact column headers and order shown in the Example tab: Date, Episode Occurred, Episode Count, Triggers Logged, Trigger Start Time, Trigger End Time, Drinks, then a repeating group of 8 columns per episode that happened that day (Episode 1 Start Time, Episode 1 End Time, Episode 1 Duration (h), Episode 1 Intensity (1-10), Episode 1 Relief Medication, Episode 1 Relief Helped, Episode 1 Suspected Cause, Episode 1 Notes — then Episode 2 …, Episode 3 …, etc. if more than one episode ever happens on the same day).
 - Date format must be YYYY-MM-DD. Times must be HH:MM in 24-hour format.
 - "Episode Occurred" is 1 if any episode happened that day, else 0. "Episode Count" is how many episodes that day.
-- "Episode X Relief Helped" must be exactly "Yes", "Somewhat", or "No".
+- "Episode X Relief Medication" can list SEVERAL medications for one episode, separated by "; " (e.g. "Excedrin; Maxalt"). Only list medications actually taken to relieve that episode — preventative medications belong on the Med Periods sheet, not here.
+- "Episode X Relief Helped" is a score from 0 to 10 for how much the medication helped: 0 = didn't help at all, 10 = completely resolved it. If several medications are listed, give one score per medication in the SAME ORDER, separated by "; " (e.g. "4; 9" means Excedrin scored 4 and Maxalt scored 9). Leave it blank if no relief medication was taken or no effect was recorded. Convert whatever my data uses: a percentage divides by 10 (80% → 8, 45% → 4.5 rounded to 5); the words "Yes"/"Somewhat"/"No" become 10/8/0; a 1–5 scale multiplies by 2. Tell me which conversion you used.
+- "Episode X Notes" is optional free text — any comment I recorded about that specific episode (how it felt, what I was doing, anything unusual). If my old data has a notes, comments, or description field tied to an episode, put it here. Keep it short; don't invent notes where none existed.
 - If you're not sure which existing field maps to "Suspected Cause" vs. a logged "Trigger", make a reasonable judgment call and note it in your reply so I can double check.
 - If my old data includes when I started or stopped taking any preventative medication, put that in a separate "Med Periods" sheet with columns Condition, Medication, Start, End (blank End = still taking it), following the Med Periods Template tab. Don't try to cram medication history into the daily columns.
 - Intensity should be on a 1-10 scale — if my old data uses a different scale (like 1-5), convert it proportionally and tell me what conversion you used.
+- A row with an intensity of 0 and no episode is NOT an episode. Many trackers record 0 (or blank) pain on symptom-free days — for those days leave the episode columns blank and set "Episode Occurred" to 0. Only create an episode where my data actually records one (e.g. "Flare today? = Yes"). Such a day can still be a trigger day, so keep its Triggers Logged and Drinks values.
+- Drop any columns from my old data that TrackDX doesn't use. Don't add extra columns of your own, and don't keep unmapped fields "just in case" — anything outside the layout above will be ignored on import.
+- Delete the example rows from the template before you hand the file back, and rename each sheet to the condition it holds.
 When you're done, give me the finished file as a downloadable .xlsx, and briefly summarize any assumptions or judgment calls you made so I can review them before I import it.</t>
         </is>
       </c>
@@ -707,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1007,12 +1015,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Medication name</t>
+          <t>Medication name(s), separated by "; "</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>What you took for relief, if anything.</t>
+          <t>What you took to relieve this episode. Several are allowed, e.g. "Excedrin; Maxalt". Preventatives go on the Med Periods sheet instead.</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1037,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>"Yes", "Somewhat", or "No"</t>
+          <t>Score 0–10, separated by "; "</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Whether the relief medication worked.</t>
+          <t>0 = didn’t help at all, 10 = completely resolved it. One score per medication listed, in the same order (e.g. "4; 9").</t>
         </is>
       </c>
     </row>
@@ -1063,34 +1071,57 @@
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>Episode 1 Notes</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Free text</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Anything you noted about this specific episode. Keep it short.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t>Episode 2 …, Episode 3 …</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Same 7 columns, repeated</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Only needed if more than one episode can happen on the same day. Repeat the group of 7 columns, numbering it up (Episode 2 Start Time, Episode 2 End Time, …).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Same 8 columns, repeated</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Only needed if more than one episode can happen on the same day. Repeat the group of 8 columns, numbering it up (Episode 2 Start Time, Episode 2 End Time, …).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>A note on preventative medications</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>TrackDX tracks which preventative medications you were on, and when, on a separate "Med Periods" sheet — not as daily columns. See the Med Periods Template tab.</t>
         </is>
@@ -1107,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1131,6 +1162,8 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1213,37 +1246,47 @@
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
+          <t>Episode 1 Notes</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
           <t>Episode 2 Start Time</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 End Time</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Duration (h)</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="S2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Intensity (1-10)</t>
         </is>
       </c>
-      <c r="S2" s="6" t="inlineStr">
+      <c r="T2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Relief Medication</t>
         </is>
       </c>
-      <c r="T2" s="6" t="inlineStr">
+      <c r="U2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Relief Helped</t>
         </is>
       </c>
-      <c r="U2" s="6" t="inlineStr">
+      <c r="V2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Suspected Cause</t>
+        </is>
+      </c>
+      <c r="W2" s="6" t="inlineStr">
+        <is>
+          <t>Episode 2 Notes</t>
         </is>
       </c>
     </row>
@@ -1277,6 +1320,8 @@
       <c r="S3" s="9" t="n"/>
       <c r="T3" s="9" t="n"/>
       <c r="U3" s="9" t="n"/>
+      <c r="V3" s="9" t="n"/>
+      <c r="W3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -1320,6 +1365,8 @@
       <c r="S4" s="9" t="n"/>
       <c r="T4" s="9" t="n"/>
       <c r="U4" s="9" t="n"/>
+      <c r="V4" s="9" t="n"/>
+      <c r="W4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -1366,7 +1413,7 @@
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
@@ -1374,13 +1421,19 @@
           <t>Alcohol</t>
         </is>
       </c>
-      <c r="O5" s="9" t="n"/>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>Three glasses of red wine at dinner.</t>
+        </is>
+      </c>
       <c r="P5" s="9" t="n"/>
       <c r="Q5" s="9" t="n"/>
       <c r="R5" s="9" t="n"/>
       <c r="S5" s="9" t="n"/>
       <c r="T5" s="9" t="n"/>
       <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -1428,12 +1481,12 @@
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>Excedrin</t>
+          <t>Excedrin; Maxalt</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>Somewhat</t>
+          <t>4; 9</t>
         </is>
       </c>
       <c r="N6" s="9" t="inlineStr">
@@ -1443,35 +1496,41 @@
       </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
+          <t>Woke up with it after the neighbours’ party.</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="P6" s="9" t="inlineStr">
+      <c r="Q6" s="9" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="R6" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="S6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="S6" s="9" t="inlineStr">
+      <c r="T6" s="9" t="inlineStr">
         <is>
           <t>Maxalt</t>
         </is>
       </c>
-      <c r="T6" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="U6" s="9" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V6" s="9" t="inlineStr">
+        <is>
           <t>TMJ</t>
         </is>
       </c>
+      <c r="W6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -1503,18 +1562,21 @@
       <c r="S7" s="9" t="n"/>
       <c r="T7" s="9" t="n"/>
       <c r="U7" s="9" t="n"/>
-    </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Row-by-row: 7/10 is a quiet day (nothing logged). 7/11 logs a trigger with no episode. 7/12 is a single episode where Alcohol was both the trigger and the suspected cause. 7/13 has two separate episodes in one day, so it uses both the Episode 1 and Episode 2 column groups. 7/14 is quiet again.</t>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="9" t="n"/>
+    </row>
+    <row r="8"/>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Row-by-row: 7/10 is a quiet day (nothing logged). 7/11 logs a trigger with no episode. 7/12 is a single episode where Alcohol was both the trigger and the suspected cause, and Maxalt scored 9 out of 10 for relief. 7/13 has two separate episodes in one day, so it uses both the Episode 1 and Episode 2 column groups — the first episode needed two medications, so both are listed with a score each ("Excedrin; Maxalt" and "4; 9"). 7/14 is quiet again.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A9:W9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1526,7 +1588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1550,6 +1612,8 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1632,37 +1696,47 @@
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
+          <t>Episode 1 Notes</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
           <t>Episode 2 Start Time</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 End Time</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Duration (h)</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="S2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Intensity (1-10)</t>
         </is>
       </c>
-      <c r="S2" s="6" t="inlineStr">
+      <c r="T2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Relief Medication</t>
         </is>
       </c>
-      <c r="T2" s="6" t="inlineStr">
+      <c r="U2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Relief Helped</t>
         </is>
       </c>
-      <c r="U2" s="6" t="inlineStr">
+      <c r="V2" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Suspected Cause</t>
+        </is>
+      </c>
+      <c r="W2" s="6" t="inlineStr">
+        <is>
+          <t>Episode 2 Notes</t>
         </is>
       </c>
     </row>
@@ -1688,6 +1762,8 @@
       <c r="S3" s="11" t="n"/>
       <c r="T3" s="11" t="n"/>
       <c r="U3" s="11" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n"/>
@@ -1711,6 +1787,8 @@
       <c r="S4" s="11" t="n"/>
       <c r="T4" s="11" t="n"/>
       <c r="U4" s="11" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n"/>
@@ -1734,6 +1812,8 @@
       <c r="S5" s="11" t="n"/>
       <c r="T5" s="11" t="n"/>
       <c r="U5" s="11" t="n"/>
+      <c r="V5" s="11" t="n"/>
+      <c r="W5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n"/>
@@ -1757,6 +1837,8 @@
       <c r="S6" s="11" t="n"/>
       <c r="T6" s="11" t="n"/>
       <c r="U6" s="11" t="n"/>
+      <c r="V6" s="11" t="n"/>
+      <c r="W6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n"/>
@@ -1780,6 +1862,8 @@
       <c r="S7" s="11" t="n"/>
       <c r="T7" s="11" t="n"/>
       <c r="U7" s="11" t="n"/>
+      <c r="V7" s="11" t="n"/>
+      <c r="W7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n"/>
@@ -1803,6 +1887,8 @@
       <c r="S8" s="11" t="n"/>
       <c r="T8" s="11" t="n"/>
       <c r="U8" s="11" t="n"/>
+      <c r="V8" s="11" t="n"/>
+      <c r="W8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n"/>
@@ -1826,6 +1912,8 @@
       <c r="S9" s="11" t="n"/>
       <c r="T9" s="11" t="n"/>
       <c r="U9" s="11" t="n"/>
+      <c r="V9" s="11" t="n"/>
+      <c r="W9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n"/>
@@ -1849,6 +1937,8 @@
       <c r="S10" s="11" t="n"/>
       <c r="T10" s="11" t="n"/>
       <c r="U10" s="11" t="n"/>
+      <c r="V10" s="11" t="n"/>
+      <c r="W10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -1872,6 +1962,8 @@
       <c r="S11" s="11" t="n"/>
       <c r="T11" s="11" t="n"/>
       <c r="U11" s="11" t="n"/>
+      <c r="V11" s="11" t="n"/>
+      <c r="W11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -1895,6 +1987,8 @@
       <c r="S12" s="11" t="n"/>
       <c r="T12" s="11" t="n"/>
       <c r="U12" s="11" t="n"/>
+      <c r="V12" s="11" t="n"/>
+      <c r="W12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -1918,6 +2012,8 @@
       <c r="S13" s="11" t="n"/>
       <c r="T13" s="11" t="n"/>
       <c r="U13" s="11" t="n"/>
+      <c r="V13" s="11" t="n"/>
+      <c r="W13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -1941,6 +2037,8 @@
       <c r="S14" s="11" t="n"/>
       <c r="T14" s="11" t="n"/>
       <c r="U14" s="11" t="n"/>
+      <c r="V14" s="11" t="n"/>
+      <c r="W14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n"/>
@@ -1964,6 +2062,8 @@
       <c r="S15" s="11" t="n"/>
       <c r="T15" s="11" t="n"/>
       <c r="U15" s="11" t="n"/>
+      <c r="V15" s="11" t="n"/>
+      <c r="W15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -1987,6 +2087,8 @@
       <c r="S16" s="11" t="n"/>
       <c r="T16" s="11" t="n"/>
       <c r="U16" s="11" t="n"/>
+      <c r="V16" s="11" t="n"/>
+      <c r="W16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -2010,6 +2112,8 @@
       <c r="S17" s="11" t="n"/>
       <c r="T17" s="11" t="n"/>
       <c r="U17" s="11" t="n"/>
+      <c r="V17" s="11" t="n"/>
+      <c r="W17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -2033,6 +2137,8 @@
       <c r="S18" s="11" t="n"/>
       <c r="T18" s="11" t="n"/>
       <c r="U18" s="11" t="n"/>
+      <c r="V18" s="11" t="n"/>
+      <c r="W18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -2056,6 +2162,8 @@
       <c r="S19" s="11" t="n"/>
       <c r="T19" s="11" t="n"/>
       <c r="U19" s="11" t="n"/>
+      <c r="V19" s="11" t="n"/>
+      <c r="W19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -2079,6 +2187,8 @@
       <c r="S20" s="11" t="n"/>
       <c r="T20" s="11" t="n"/>
       <c r="U20" s="11" t="n"/>
+      <c r="V20" s="11" t="n"/>
+      <c r="W20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -2102,6 +2212,8 @@
       <c r="S21" s="11" t="n"/>
       <c r="T21" s="11" t="n"/>
       <c r="U21" s="11" t="n"/>
+      <c r="V21" s="11" t="n"/>
+      <c r="W21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -2125,6 +2237,8 @@
       <c r="S22" s="11" t="n"/>
       <c r="T22" s="11" t="n"/>
       <c r="U22" s="11" t="n"/>
+      <c r="V22" s="11" t="n"/>
+      <c r="W22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -2148,6 +2262,8 @@
       <c r="S23" s="11" t="n"/>
       <c r="T23" s="11" t="n"/>
       <c r="U23" s="11" t="n"/>
+      <c r="V23" s="11" t="n"/>
+      <c r="W23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -2171,6 +2287,8 @@
       <c r="S24" s="11" t="n"/>
       <c r="T24" s="11" t="n"/>
       <c r="U24" s="11" t="n"/>
+      <c r="V24" s="11" t="n"/>
+      <c r="W24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -2194,6 +2312,8 @@
       <c r="S25" s="11" t="n"/>
       <c r="T25" s="11" t="n"/>
       <c r="U25" s="11" t="n"/>
+      <c r="V25" s="11" t="n"/>
+      <c r="W25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -2217,6 +2337,8 @@
       <c r="S26" s="11" t="n"/>
       <c r="T26" s="11" t="n"/>
       <c r="U26" s="11" t="n"/>
+      <c r="V26" s="11" t="n"/>
+      <c r="W26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -2240,6 +2362,8 @@
       <c r="S27" s="11" t="n"/>
       <c r="T27" s="11" t="n"/>
       <c r="U27" s="11" t="n"/>
+      <c r="V27" s="11" t="n"/>
+      <c r="W27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -2335,7 +2459,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/files/TrackDX-Import-Assistant.xlsx
+++ b/assets/files/TrackDX-Import-Assistant.xlsx
@@ -172,6 +172,111 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>TrackDX</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Example — the sheet name would be the condition (“Migraine”), max 15 characters.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>TrackDX</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Blank template — rename this tab to your condition's name (max 15 characters).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>TrackDX</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Example — a daily-rated condition (“Sciatica”). Note 2026-07-13 is BLANK (not recorded) while the calf on 2026-07-14 is a genuine 0.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>TrackDX</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Blank template — rename this tab to your condition's name, and rename the “Severity: …” columns to your own body locations (max 6).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>TrackDX</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Conditions — tells TrackDX which conditions are tracked daily, and their body locations. Include this sheet whenever any condition is daily.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>TrackDX</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Procedures — surgeries, injections and blocks. Leave the two “Recalled” columns blank unless the procedure happened before your logging starts.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>TrackDX</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Med Periods — which preventative medications you were on, and when (blank End = still taking it).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -683,7 +788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -693,31 +798,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Med Periods — which preventative medications you were on, and when (blank End = still taking it).</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Medication</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>End</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Medication</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>End</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Migraine</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Propranolol</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
         </is>
       </c>
     </row>
@@ -729,49 +849,27 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Propranolol</t>
+          <t>Botox</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Migraine</t>
+          <t>Sciatica</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Botox</t>
+          <t>Gabapentin</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Sciatica</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Gabapentin</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
@@ -779,6 +877,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -821,6 +920,7 @@
 Then convert my data. For BOTH kinds:
 - Create ONE sheet per condition, named with the condition's name (max 15 characters — that's Excel's tab-name rule TrackDX follows).
 - ONE ROW PER CALENDAR DAY, from the earliest date in my data through today, INCLUDING days with nothing logged. The empty days are real information to TrackDX's statistics, so don't skip them.
+- PUT THE COLUMN HEADERS IN THE VERY FIRST ROW of each sheet. No title, caption or blank row above them — TrackDX reads row 1 as the header and stops, so anything above it makes the whole sheet import as empty.
 - Date format must be YYYY-MM-DD. Times must be HH:MM in 24-hour format.
 - Don't add columns of your own, and don't keep unmapped fields "just in case" — anything outside the layouts below is ignored on import.
 - Delete the template's example rows before handing the file back.
@@ -1867,7 +1967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1897,138 +1997,144 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Example — the sheet name would be the condition (“Migraine”), max 15 characters.</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Episode Occurred</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Episode Count</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Triggers Logged</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Trigger Start Time</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Trigger End Time</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Drink Type</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 1 Start Time</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 1 End Time</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 1 Duration (h)</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 1 Intensity (1-10)</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 1 Relief Medication</t>
+        </is>
+      </c>
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 1 Relief Helped</t>
+        </is>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 1 Suspected Cause</t>
+        </is>
+      </c>
+      <c r="P1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 1 Notes</t>
+        </is>
+      </c>
+      <c r="Q1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 2 Start Time</t>
+        </is>
+      </c>
+      <c r="R1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 2 End Time</t>
+        </is>
+      </c>
+      <c r="S1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 2 Duration (h)</t>
+        </is>
+      </c>
+      <c r="T1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 2 Intensity (1-10)</t>
+        </is>
+      </c>
+      <c r="U1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 2 Relief Medication</t>
+        </is>
+      </c>
+      <c r="V1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 2 Relief Helped</t>
+        </is>
+      </c>
+      <c r="W1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 2 Suspected Cause</t>
+        </is>
+      </c>
+      <c r="X1" s="6" t="inlineStr">
+        <is>
+          <t>Episode 2 Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Episode Occurred</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Episode Count</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Triggers Logged</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Trigger Start Time</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>Trigger End Time</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Drinks</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Drink Type</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 1 Start Time</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 1 End Time</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 1 Duration (h)</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 1 Intensity (1-10)</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 1 Relief Medication</t>
-        </is>
-      </c>
-      <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 1 Relief Helped</t>
-        </is>
-      </c>
-      <c r="O2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 1 Suspected Cause</t>
-        </is>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 1 Notes</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 2 Start Time</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 2 End Time</t>
-        </is>
-      </c>
-      <c r="S2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 2 Duration (h)</t>
-        </is>
-      </c>
-      <c r="T2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 2 Intensity (1-10)</t>
-        </is>
-      </c>
-      <c r="U2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 2 Relief Medication</t>
-        </is>
-      </c>
-      <c r="V2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 2 Relief Helped</t>
-        </is>
-      </c>
-      <c r="W2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 2 Suspected Cause</t>
-        </is>
-      </c>
-      <c r="X2" s="6" t="inlineStr">
-        <is>
-          <t>Episode 2 Notes</t>
-        </is>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
@@ -2037,203 +2143,191 @@
       <c r="C3" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Stress</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Stress</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>Alcohol</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Red wine</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Maxalt</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>Alcohol</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>Three glasses of red wine at dinner.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Alcohol</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
+          <t>Sound; TMJ</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Red wine</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
+      <c r="L5" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Excedrin; Maxalt</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>4; 9</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Woke up with it after the neighbours' party.</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="L5" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Maxalt</t>
         </is>
       </c>
-      <c r="N5" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>Alcohol</t>
-        </is>
-      </c>
-      <c r="P5" s="7" t="inlineStr">
-        <is>
-          <t>Three glasses of red wine at dinner.</t>
+      <c r="V5" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>TMJ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Sound; TMJ</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>Excedrin; Maxalt</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>4; 9</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>Sound</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>Woke up with it after the neighbours' party.</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>Maxalt</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
-        <is>
-          <t>TMJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2243,7 +2337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2273,129 +2367,122 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Blank template — rename this tab to your condition's name (max 15 characters).</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Episode Occurred</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Episode Count</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Triggers Logged</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Trigger Start Time</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Trigger End Time</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Drinks</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Drink Type</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Episode 1 Start Time</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Episode 1 End Time</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Episode 1 Duration (h)</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Episode 1 Intensity (1-10)</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Episode 1 Relief Medication</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Episode 1 Relief Helped</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Episode 1 Suspected Cause</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Episode 1 Notes</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Start Time</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>Episode 2 End Time</t>
         </is>
       </c>
-      <c r="S2" s="6" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Duration (h)</t>
         </is>
       </c>
-      <c r="T2" s="6" t="inlineStr">
+      <c r="T1" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Intensity (1-10)</t>
         </is>
       </c>
-      <c r="U2" s="6" t="inlineStr">
+      <c r="U1" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Relief Medication</t>
         </is>
       </c>
-      <c r="V2" s="6" t="inlineStr">
+      <c r="V1" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Relief Helped</t>
         </is>
       </c>
-      <c r="W2" s="6" t="inlineStr">
+      <c r="W1" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Suspected Cause</t>
         </is>
       </c>
-      <c r="X2" s="6" t="inlineStr">
+      <c r="X1" s="6" t="inlineStr">
         <is>
           <t>Episode 2 Notes</t>
         </is>
@@ -2403,6 +2490,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2412,7 +2500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2428,152 +2516,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Example — a daily-rated condition (“Sciatica”). Note 2026-07-13 is BLANK (not recorded) while the calf on 2026-07-14 is a genuine 0.</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Triggers Logged</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Trigger Start Time</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Trigger End Time</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Drinks</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Drink Type</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Severity: Lower back</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Severity: Right hip</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Severity: Right calf</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Triggers Logged</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Trigger Start Time</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Trigger End Time</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Drinks</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>Drink Type</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Severity: Lower back</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Severity: Right hip</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Severity: Right calf</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Baseline before the injection.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Running</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G3" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="H3" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="I3" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Baseline before the injection.</t>
-        </is>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Running</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>4</v>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Didn't rate today — blank, NOT zero.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Didn't rate today — blank, NOT zero.</t>
+          <t>Day after the injection. Calf genuinely clear, so 0 not blank.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Poor sleep</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Beer</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>2</v>
@@ -2581,43 +2696,10 @@
       <c r="I7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Day after the injection. Calf genuinely clear, so 0 not blank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Poor sleep</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Beer</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2627,7 +2709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2643,59 +2725,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Blank template — rename this tab to your condition's name, and rename the “Severity: …” columns to your own body locations (max 6).</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Triggers Logged</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Trigger Start Time</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Trigger End Time</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Drinks</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Drink Type</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Severity: Lower back</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Severity: Right hip</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Severity: Right calf</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2703,6 +2778,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2712,7 +2788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2721,53 +2797,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Conditions — tells TrackDX which conditions are tracked daily, and their body locations. Include this sheet whenever any condition is daily.</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Tracking Mode</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Sites</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Tracking Mode</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Sites</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Sciatica</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Lower back; Right hip; Right calf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Sciatica</t>
+          <t>Migraine</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Lower back; Right hip; Right calf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Migraine</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Episodes</t>
         </is>
@@ -2775,6 +2844,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2784,7 +2854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2797,46 +2867,66 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Procedures — surgeries, injections and blocks. Leave the two “Recalled” columns blank unless the procedure happened before your logging starts.</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Recalled Overall</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Recalled By Site</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Procedure</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>Recalled Overall</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Recalled By Site</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Sciatica</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>L4-L5 epidural injection</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Lower back</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Second of a planned series.</t>
         </is>
       </c>
     </row>
@@ -2848,52 +2938,25 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>L4-L5 epidural injection</t>
+          <t>Piriformis injection</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Lower back</t>
+          <t>Right hip</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Second of a planned series.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Sciatica</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Piriformis injection</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Right hip</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
           <t>Before I started logging — numbers below are from memory.</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Lower back=7; Right hip=8; Right calf=5</t>
         </is>
@@ -2901,5 +2964,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>